--- a/panchang-data/Montreal_Quebec2026.xlsx
+++ b/panchang-data/Montreal_Quebec2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5420">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16285,6 +16285,9 @@
   </si>
   <si>
     <t>121°03'35.05</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16774,7 +16777,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16860,7 +16863,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>52</v>
@@ -16946,7 +16949,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>72</v>
@@ -17032,7 +17035,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>92</v>
@@ -17118,7 +17121,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>109</v>
@@ -17204,7 +17207,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>127</v>
@@ -17290,7 +17293,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>145</v>
@@ -17376,7 +17379,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17462,7 +17465,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>52</v>
@@ -17548,7 +17551,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>72</v>
@@ -17634,7 +17637,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>92</v>
@@ -17720,7 +17723,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>109</v>
@@ -17806,7 +17809,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>127</v>
@@ -17892,7 +17895,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>145</v>
@@ -17978,7 +17981,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -18064,7 +18067,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>52</v>
@@ -18150,7 +18153,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>72</v>
@@ -18236,7 +18239,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>92</v>
@@ -18322,7 +18325,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>109</v>
@@ -18408,7 +18411,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>127</v>
@@ -18494,7 +18497,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>145</v>
@@ -18580,7 +18583,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18666,7 +18669,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>52</v>
@@ -18752,7 +18755,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>72</v>
@@ -18838,7 +18841,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>92</v>
@@ -18924,7 +18927,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>109</v>
@@ -19010,7 +19013,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>127</v>
@@ -19096,7 +19099,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>145</v>
@@ -19182,7 +19185,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19268,7 +19271,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>52</v>
@@ -19354,7 +19357,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>72</v>
@@ -19440,7 +19443,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>92</v>
@@ -19526,7 +19529,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>109</v>
@@ -19612,7 +19615,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>127</v>
@@ -19698,7 +19701,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>145</v>
@@ -19784,7 +19787,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19870,7 +19873,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>52</v>
@@ -19956,7 +19959,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>72</v>
@@ -20042,7 +20045,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>92</v>
@@ -20128,7 +20131,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>109</v>
@@ -20214,7 +20217,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>127</v>
@@ -20300,7 +20303,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>145</v>
@@ -20386,7 +20389,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20472,7 +20475,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>52</v>
@@ -20558,7 +20561,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>72</v>
@@ -20644,7 +20647,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>92</v>
@@ -20730,7 +20733,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>109</v>
@@ -20816,7 +20819,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>127</v>
@@ -20902,7 +20905,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>145</v>
@@ -20988,7 +20991,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -21074,7 +21077,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>52</v>
@@ -21160,7 +21163,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>72</v>
@@ -21246,7 +21249,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>92</v>
@@ -21332,7 +21335,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>109</v>
@@ -21418,7 +21421,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>127</v>
@@ -21504,7 +21507,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>145</v>
@@ -21590,7 +21593,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21676,7 +21679,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>52</v>
@@ -21762,7 +21765,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>72</v>
@@ -21848,7 +21851,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>92</v>
@@ -21934,7 +21937,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>571</v>
+        <v>1001</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>109</v>
@@ -22020,7 +22023,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>127</v>
@@ -22106,7 +22109,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>145</v>
@@ -22192,7 +22195,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22278,7 +22281,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>52</v>
@@ -22364,7 +22367,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>72</v>
@@ -22450,7 +22453,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>92</v>
@@ -22536,7 +22539,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>109</v>
@@ -22622,7 +22625,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>127</v>
@@ -22708,7 +22711,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>145</v>
@@ -22794,7 +22797,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22880,7 +22883,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>52</v>
@@ -22966,7 +22969,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>72</v>
@@ -23052,7 +23055,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>92</v>
@@ -23138,7 +23141,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>109</v>
@@ -23224,7 +23227,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>127</v>
@@ -23310,7 +23313,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>145</v>
@@ -23396,7 +23399,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23482,7 +23485,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>52</v>
@@ -23568,7 +23571,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>72</v>
@@ -23654,7 +23657,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>92</v>
@@ -23740,7 +23743,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>109</v>
@@ -23826,7 +23829,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>127</v>
@@ -23912,7 +23915,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>145</v>
@@ -23998,7 +24001,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -24084,7 +24087,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>52</v>
@@ -24170,7 +24173,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>72</v>
@@ -24256,7 +24259,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>92</v>
@@ -24342,7 +24345,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>109</v>
@@ -24428,7 +24431,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>127</v>
@@ -24514,7 +24517,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1001</v>
+        <v>1442</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>145</v>
@@ -24600,7 +24603,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24686,7 +24689,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>52</v>
@@ -24772,7 +24775,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>72</v>
@@ -24858,7 +24861,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>92</v>
@@ -24944,7 +24947,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>109</v>
@@ -25030,7 +25033,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>127</v>
@@ -25116,7 +25119,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>145</v>
@@ -25202,7 +25205,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25288,7 +25291,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>52</v>
@@ -25374,7 +25377,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>72</v>
@@ -25460,7 +25463,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>92</v>
@@ -25546,7 +25549,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>109</v>
@@ -25632,7 +25635,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>127</v>
@@ -25718,7 +25721,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>145</v>
@@ -25804,7 +25807,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25890,7 +25893,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>52</v>
@@ -25976,7 +25979,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>72</v>
@@ -26062,7 +26065,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>92</v>
@@ -26148,7 +26151,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>109</v>
@@ -26234,7 +26237,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>127</v>
@@ -26320,7 +26323,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>145</v>
@@ -26406,7 +26409,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26492,7 +26495,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>52</v>
@@ -26578,7 +26581,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>72</v>
@@ -26664,7 +26667,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>92</v>
@@ -26750,7 +26753,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>109</v>
@@ -26836,7 +26839,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>127</v>
@@ -26922,7 +26925,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>145</v>
@@ -27008,7 +27011,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27094,7 +27097,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1442</v>
+        <v>1880</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>52</v>
@@ -27180,7 +27183,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1880</v>
+        <v>2303</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>72</v>
@@ -27266,7 +27269,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1880</v>
+        <v>2303</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>92</v>
@@ -27352,7 +27355,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1880</v>
+        <v>2303</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>109</v>
@@ -27438,7 +27441,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1880</v>
+        <v>2303</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>127</v>
@@ -27524,7 +27527,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1880</v>
+        <v>2303</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>145</v>
@@ -27610,7 +27613,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1880</v>
+        <v>2303</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27696,7 +27699,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1880</v>
+        <v>2303</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>52</v>
@@ -27782,7 +27785,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1880</v>
+        <v>2303</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>72</v>
@@ -27868,7 +27871,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1880</v>
+        <v>2303</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>92</v>
@@ -27954,7 +27957,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1880</v>
+        <v>2303</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>109</v>
@@ -28040,7 +28043,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1880</v>
+        <v>2303</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>127</v>
@@ -28126,7 +28129,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1880</v>
+        <v>2303</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>145</v>
@@ -28212,7 +28215,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1880</v>
+        <v>2303</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28298,7 +28301,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1880</v>
+        <v>2303</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>52</v>
@@ -28384,7 +28387,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1880</v>
+        <v>2303</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>72</v>
@@ -28470,7 +28473,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1880</v>
+        <v>5419</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>92</v>
@@ -28556,7 +28559,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1880</v>
+        <v>5419</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>109</v>
@@ -28642,7 +28645,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1880</v>
+        <v>5419</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>127</v>
@@ -28728,7 +28731,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1880</v>
+        <v>5419</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>145</v>
@@ -28814,7 +28817,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1880</v>
+        <v>5419</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28900,7 +28903,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1880</v>
+        <v>5419</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>52</v>
@@ -28986,7 +28989,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1880</v>
+        <v>5419</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>72</v>
@@ -29072,7 +29075,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1880</v>
+        <v>5419</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>92</v>
@@ -29158,7 +29161,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1880</v>
+        <v>5419</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>109</v>
@@ -29244,7 +29247,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1880</v>
+        <v>5419</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>127</v>
@@ -29330,7 +29333,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1880</v>
+        <v>5419</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>145</v>
@@ -29416,7 +29419,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1880</v>
+        <v>5419</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29502,7 +29505,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1880</v>
+        <v>5419</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>52</v>
@@ -29588,7 +29591,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1880</v>
+        <v>5419</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>72</v>
@@ -29674,7 +29677,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>2303</v>
+        <v>5419</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>92</v>
@@ -29760,7 +29763,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2303</v>
+        <v>5419</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>109</v>
@@ -29846,7 +29849,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2303</v>
+        <v>5419</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>127</v>
@@ -29932,7 +29935,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2303</v>
+        <v>5419</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>145</v>
@@ -30018,7 +30021,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2303</v>
+        <v>5419</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30104,7 +30107,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2303</v>
+        <v>5419</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>52</v>
@@ -30190,7 +30193,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2303</v>
+        <v>5419</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>72</v>
@@ -30276,7 +30279,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2303</v>
+        <v>5419</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>92</v>
@@ -30362,7 +30365,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2303</v>
+        <v>5419</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>109</v>
@@ -30448,7 +30451,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2303</v>
+        <v>5419</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>127</v>
@@ -30534,7 +30537,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2303</v>
+        <v>5419</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>145</v>
@@ -30620,7 +30623,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2303</v>
+        <v>5419</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30706,7 +30709,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2303</v>
+        <v>5419</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>52</v>
@@ -30792,7 +30795,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2303</v>
+        <v>5419</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>72</v>
@@ -30878,7 +30881,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2303</v>
+        <v>5419</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>92</v>
